--- a/test/list/rajadesa/sukaharja/list_sukaharja_2.xlsx
+++ b/test/list/rajadesa/sukaharja/list_sukaharja_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\rajadesa\sukaharja\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0CE94-70F0-43B0-B261-7602AADC5FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5238A0D-8884-4A95-8020-65293B005BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -16,17 +16,28 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="conf" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="147">
   <si>
     <t>nama</t>
   </si>
@@ -169,64 +180,304 @@
     <t>Kurangnya perhatian terhadap isu lingkungan dan keberlanjutan, menciptakan ketidakpastian akan masa depan lingkungan hidup.</t>
   </si>
   <si>
-    <t>SOLIHAT</t>
-  </si>
-  <si>
-    <t>2023-09-05</t>
-  </si>
-  <si>
-    <t>2023-09-06</t>
-  </si>
-  <si>
-    <t>2023-09-07</t>
-  </si>
-  <si>
-    <t>2023-09-08</t>
-  </si>
-  <si>
-    <t>SALSA NUR AMELIA</t>
-  </si>
-  <si>
-    <t>TOTO HARYANTO</t>
-  </si>
-  <si>
-    <t>NIA KURNIASIH</t>
-  </si>
-  <si>
-    <t>SIFA MAWARDAH</t>
-  </si>
-  <si>
-    <t>KHOIRUNNISA</t>
-  </si>
-  <si>
-    <t>RUSTINI</t>
-  </si>
-  <si>
-    <t>ASEP SOBARI</t>
-  </si>
-  <si>
-    <t>ARIP HIDAYAT</t>
-  </si>
-  <si>
-    <t>SOLEH HIDAYAT</t>
-  </si>
-  <si>
-    <t>ICIH</t>
-  </si>
-  <si>
-    <t>UUS HUSNI MUBAROK</t>
-  </si>
-  <si>
-    <t>ANTINAH</t>
-  </si>
-  <si>
-    <t>DUDUNG</t>
-  </si>
-  <si>
-    <t>NANDA RAMDANI</t>
-  </si>
-  <si>
-    <t>ENOH</t>
+    <t>2023-10-10</t>
+  </si>
+  <si>
+    <t>2023-10-11</t>
+  </si>
+  <si>
+    <t>2023-10-12</t>
+  </si>
+  <si>
+    <t>2023-10-13</t>
+  </si>
+  <si>
+    <t>2023-10-14</t>
+  </si>
+  <si>
+    <t>2023-10-16</t>
+  </si>
+  <si>
+    <t>2023-10-17</t>
+  </si>
+  <si>
+    <t>2023-10-18</t>
+  </si>
+  <si>
+    <t>2023-10-19</t>
+  </si>
+  <si>
+    <t>2023-10-20</t>
+  </si>
+  <si>
+    <t>2023-10-21</t>
+  </si>
+  <si>
+    <t>2023-10-23</t>
+  </si>
+  <si>
+    <t>2023-10-24</t>
+  </si>
+  <si>
+    <t>Banyak masyarakat yang merasa khawatir karena harga pangan yang sering berfluktuasi dan sulit diprediksi.</t>
+  </si>
+  <si>
+    <t>menurut $nama Banyak masyarakat yang merasa khawatir karena harga pangan yang sering berfluktuasi dan sulit diprediksi.</t>
+  </si>
+  <si>
+    <t>Harga kebutuhan pokok naik terus, sulit untuk mencukupi kebutuhan sehari-hari.</t>
+  </si>
+  <si>
+    <t>Pekerjaan sulit dicari, pengangguran meningkat di wilayah ini.</t>
+  </si>
+  <si>
+    <t>Biaya pendidikan mahal, sulit bagi keluarga kurang mampu.</t>
+  </si>
+  <si>
+    <t>Persaingan usaha tidak sehat, usaha kecil sulit bertahan.</t>
+  </si>
+  <si>
+    <t>Banyak produk palsu, merugikan konsumen dan produsen asli.</t>
+  </si>
+  <si>
+    <t>Upah minimum rendah, sulit untuk hidup layak bagi warga.</t>
+  </si>
+  <si>
+    <t>Birokrasi perizinan usaha sulit dan memakan waktu.</t>
+  </si>
+  <si>
+    <t>Ketimpangan sosial dan ekonomi semakin besar, kesenjangan kaya-miskin.</t>
+  </si>
+  <si>
+    <t>Jalan rusak parah, mengganggu kelancaran lalu lintas dan merusak kendaraan.</t>
+  </si>
+  <si>
+    <t>Kemacetan lalu lintas yang parah, menyebabkan waktu tempuh yang lama.</t>
+  </si>
+  <si>
+    <t>Kurangnya perawatan rutin, membuat jalan semakin buruk.</t>
+  </si>
+  <si>
+    <t>Kurangnya penyeberangan pejalan kaki dan fasilitas untuk penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Kebutuhan perluasan jalan tidak terpenuhi, menyebabkan kemacetan terus bertambah.</t>
+  </si>
+  <si>
+    <t>Kurangnya penerangan jalan yang memadai, meningkatkan risiko kecelakaan di malam hari.</t>
+  </si>
+  <si>
+    <t>Jalan berlubang yang berbahaya bagi pengendara sepeda motor dan pengguna jalan lainnya.</t>
+  </si>
+  <si>
+    <t>Kurangnya trotoar yang aman, mengancam keselamatan pejalan kaki.</t>
+  </si>
+  <si>
+    <t>Parkir liar yang menghalangi akses jalan dan mengurangi ruang untuk kendaraan.</t>
+  </si>
+  <si>
+    <t>Kurangnya rambu lalu lintas yang jelas dan terawat, membingungkan pengguna jalan.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jalur sepeda yang aman, menghambat pengembangan transportasi berkelanjutan.</t>
+  </si>
+  <si>
+    <t>Kendaraan parkir sembarangan di jalan, menyebabkan kemacetan dan kekacauan.</t>
+  </si>
+  <si>
+    <t>Jalan tidak terlayani saat hujan, menyebabkan banjir dan genangan air.</t>
+  </si>
+  <si>
+    <t>Tidak adanya fasilitas penyeberangan untuk hewan di jalan raya.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>Jalan tidak ramah lingkungan, tanpa pohon atau taman penyerap polusi.</t>
+  </si>
+  <si>
+    <t>Marka jalan yang pudar atau tidak terlihat jelas, meningkatkan risiko kecelakaan.</t>
+  </si>
+  <si>
+    <t>Kurangnya jalan alternatif untuk mengurangi kepadatan lalu lintas di ruas jalan utama.</t>
+  </si>
+  <si>
+    <t>PURMAN AS</t>
+  </si>
+  <si>
+    <t>ENUNG NINING</t>
+  </si>
+  <si>
+    <t>MUHLIS</t>
+  </si>
+  <si>
+    <t>ATIN KURNIATIN</t>
+  </si>
+  <si>
+    <t>RAYSA AMELIA PUTRI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD RIFKI HAIDAR</t>
+  </si>
+  <si>
+    <t>ABDUL KARIM</t>
+  </si>
+  <si>
+    <t>TITIN SUPRIATIN</t>
+  </si>
+  <si>
+    <t>ZAHRA LAILA</t>
+  </si>
+  <si>
+    <t>RIAN ADITIA</t>
+  </si>
+  <si>
+    <t>KEYO</t>
+  </si>
+  <si>
+    <t>SARI ERNA NURSAFITRI</t>
+  </si>
+  <si>
+    <t>H. TOHIR</t>
+  </si>
+  <si>
+    <t>ANAH</t>
+  </si>
+  <si>
+    <t>DARUSMAN</t>
+  </si>
+  <si>
+    <t>NANI ROHANI</t>
+  </si>
+  <si>
+    <t>DELLA PADIA HANUM</t>
+  </si>
+  <si>
+    <t>FIRNANDA ZAYNA AL MASFHUFAH</t>
+  </si>
+  <si>
+    <t>JAMAL ABDUN NANGER</t>
+  </si>
+  <si>
+    <t>LILIS SOFWATI</t>
+  </si>
+  <si>
+    <t>MUTIARA SYAHIDAH</t>
+  </si>
+  <si>
+    <t>NUR BADRIAH</t>
+  </si>
+  <si>
+    <t>ENGKOS</t>
+  </si>
+  <si>
+    <t>MAMAH</t>
+  </si>
+  <si>
+    <t>RIKA NURHOERUNNISA</t>
+  </si>
+  <si>
+    <t>ROMLI</t>
+  </si>
+  <si>
+    <t>MARIAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD AGUS ABDUL NURIDO</t>
+  </si>
+  <si>
+    <t>MUTIAH</t>
+  </si>
+  <si>
+    <t>TARWA</t>
+  </si>
+  <si>
+    <t>OYOH</t>
+  </si>
+  <si>
+    <t>ABDULAH</t>
+  </si>
+  <si>
+    <t>NETI</t>
+  </si>
+  <si>
+    <t>TUTI RUSMAYANTI</t>
+  </si>
+  <si>
+    <t>LIRA</t>
+  </si>
+  <si>
+    <t>DIKY MAWARDI</t>
+  </si>
+  <si>
+    <t>BERI NUGRAHA</t>
+  </si>
+  <si>
+    <t>REVA</t>
+  </si>
+  <si>
+    <t>MAS`UD</t>
+  </si>
+  <si>
+    <t>SITI MAEMUNAH</t>
+  </si>
+  <si>
+    <t>RIFANTI</t>
+  </si>
+  <si>
+    <t>ALIFA MARYANI</t>
+  </si>
+  <si>
+    <t>HAMID</t>
+  </si>
+  <si>
+    <t>SAWIT</t>
+  </si>
+  <si>
+    <t>TIA MARYANI</t>
+  </si>
+  <si>
+    <t>JAELANI</t>
+  </si>
+  <si>
+    <t>KUSWATI</t>
+  </si>
+  <si>
+    <t>ZIANKA MAULANA PUTRA</t>
+  </si>
+  <si>
+    <t>ZIHAD MUHAMAD NUR RIZKI</t>
+  </si>
+  <si>
+    <t>KARTIWA</t>
+  </si>
+  <si>
+    <t>SITI HODIJAH</t>
+  </si>
+  <si>
+    <t>KIKI HIDAYANTI</t>
+  </si>
+  <si>
+    <t>RUSLAN</t>
+  </si>
+  <si>
+    <t>DARMI RATNASARI</t>
+  </si>
+  <si>
+    <t>MUHAMAD LUTFI FAUZIAH HIMAWAN</t>
   </si>
 </sst>
 </file>
@@ -234,7 +485,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -283,16 +534,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Mata Uang" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -309,7 +563,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -605,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330EDF8F-AF7E-4CFD-AD2A-76F45302569C}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" style="1" customWidth="1"/>
@@ -646,29 +900,29 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar</v>
+        <v>Cikawung</v>
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>004</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>007</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -676,29 +930,29 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar</v>
+        <v>Cihawar Mekarsari</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>005</v>
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>002</v>
       </c>
       <c r="G3" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -706,10 +960,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -717,18 +971,18 @@
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>005</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>015</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H4" t="s">
-        <v>33</v>
+      <c r="H4" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -736,18 +990,18 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar</v>
+        <v>Cihawar Mekarsari</v>
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>001</v>
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -757,8 +1011,8 @@
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H5" t="s">
-        <v>34</v>
+      <c r="H5" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -766,29 +1020,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar</v>
+        <v>Ciri Mekarharja</v>
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>003</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>009</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H6" t="s">
-        <v>35</v>
+      <c r="H6" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -796,29 +1050,29 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Ciri Mekarharja</v>
+        <v>Cikawung</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>004</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>013</v>
       </c>
       <c r="G7" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H7" t="s">
-        <v>36</v>
+      <c r="H7" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -826,29 +1080,29 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikawung</v>
+        <v>Cihawar</v>
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>006</v>
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>004</v>
       </c>
       <c r="G8" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H8" t="s">
-        <v>37</v>
+      <c r="H8" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -856,29 +1110,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar</v>
+        <v>Cikawung</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>003</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>008</v>
       </c>
       <c r="G9" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H9" t="s">
-        <v>38</v>
+      <c r="H9" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -886,10 +1140,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -897,18 +1151,18 @@
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>012</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>008</v>
       </c>
       <c r="G10" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H10" t="s">
-        <v>39</v>
+      <c r="H10" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -916,29 +1170,29 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar Mekarsari</v>
+        <v>Cihawar</v>
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>010</v>
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>010</v>
       </c>
       <c r="G11" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H11" t="s">
-        <v>40</v>
+      <c r="H11" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -946,14 +1200,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar Mekarsari</v>
+        <v>Cikawung</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -961,14 +1215,14 @@
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>013</v>
       </c>
       <c r="G12" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -976,29 +1230,29 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar Mekarsari</v>
+        <v>Cikawung</v>
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>008</v>
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="G13" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H13" t="s">
-        <v>42</v>
+      <c r="H13" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1006,29 +1260,29 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cihawar</v>
+        <v>Ciri Mekarharja</v>
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>005</v>
       </c>
-      <c r="F14" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
-      </c>
       <c r="G14" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H14" t="s">
-        <v>43</v>
+      <c r="H14" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1036,29 +1290,29 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikawung</v>
+        <v>Cihawar</v>
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>013</v>
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>009</v>
       </c>
       <c r="G15" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H15" t="s">
-        <v>44</v>
+      <c r="H15" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1066,29 +1320,29 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikawung</v>
+        <v>Cihawar Mekarsari</v>
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="G16" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sukaharja</v>
       </c>
-      <c r="H16" t="s">
-        <v>45</v>
+      <c r="H16" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1096,58 +1350,1110 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="2" t="str">
+      <c r="C18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Ciri Mekarharja</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
         <v>Cikawung</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+      <c r="E19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>001</v>
       </c>
-      <c r="F17" s="2" t="str">
+      <c r="G23" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Ciri Mekarharja</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>006</v>
       </c>
-      <c r="G17" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v>Sukaharja</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="G33" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G34" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G35" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G36" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G37" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G38" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G39" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G40" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G41" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H41" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="3"/>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G42" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G43" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G44" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Ciri Mekarharja</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G45" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H45" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Ciri Mekarharja</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G46" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H46" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G47" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G48" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G49" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G50" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Ciri Mekarharja</v>
+      </c>
+      <c r="E51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G51" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H51" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G52" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar Mekarsari</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G53" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikawung</v>
+      </c>
+      <c r="E54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G54" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H54" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G55" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H55" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Ciri Mekarharja</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G56" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H56" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B57" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cihawar</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G57" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sukaharja</v>
+      </c>
+      <c r="H57" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
